--- a/notebooks/results/network_name=Q1_zonal__dc_allocation=1__total_dc_gw=4__flexibility_fraction=0.1.xlsx
+++ b/notebooks/results/network_name=Q1_zonal__dc_allocation=1__total_dc_gw=4__flexibility_fraction=0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marta/Documents/MSc CAM/Dissertation/PyPSA-GB/notebooks/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A689B6F6-46D0-6A4A-B048-90835DECBCE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E341DBF4-7C57-D74A-8B52-DD974E576D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17400" activeTab="3" xr2:uid="{D4188A73-9F76-7B43-A2AE-82D891E862BC}"/>
+    <workbookView xWindow="4080" yWindow="600" windowWidth="30240" windowHeight="17400" activeTab="3" xr2:uid="{D4188A73-9F76-7B43-A2AE-82D891E862BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Inflexible" sheetId="4" r:id="rId1"/>
@@ -20,9 +20,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Both!$A$1:$N$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Inflexible!$A$1:$N$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Spatial!$A$1:$N$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Temporal!$A$1:$N$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Inflexible!$A$1:$N$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Spatial!$A$1:$N$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Temporal!$A$1:$N$35</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="57">
   <si>
     <t>Optimal Capacity</t>
   </si>
@@ -207,6 +207,18 @@
   </si>
   <si>
     <t>total:</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>Total Green Energy curtailment:</t>
+  </si>
+  <si>
+    <t>Total Wind Energy Curtailment:</t>
+  </si>
+  <si>
+    <t>Total Green Capacity:</t>
   </si>
 </sst>
 </file>
@@ -698,11 +710,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4972E32-7E17-D640-8808-61170EE7E9D2}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5" customWidth="1"/>
+    <col min="2" max="2" width="19.5" customWidth="1"/>
     <col min="3" max="3" width="21.33203125" customWidth="1"/>
     <col min="4" max="4" width="22.6640625" customWidth="1"/>
   </cols>
@@ -875,7 +887,7 @@
         <v>80.533528000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
       <c r="B5" s="1" t="s">
         <v>16</v>
@@ -917,7 +929,7 @@
         <v>84.755994000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="30" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="6"/>
       <c r="B6" s="1" t="s">
         <v>17</v>
@@ -1211,7 +1223,7 @@
         <v>6001.0768930000004</v>
       </c>
     </row>
-    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="1" t="s">
         <v>25</v>
@@ -1295,7 +1307,7 @@
         <v>66.309685000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
       <c r="B15" s="1" t="s">
         <v>27</v>
@@ -1379,7 +1391,7 @@
         <v>66.320971</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="30" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
       <c r="B17" s="1" t="s">
         <v>29</v>
@@ -2006,7 +2018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="9:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="I33" s="14" t="s">
         <v>51</v>
       </c>
@@ -2015,37 +2027,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="2">
+        <f>SUMIFS($D$2:$D$32,$B$2:$B$32, "Solar PV")+SUMIFS($D$2:$D$32,$B$2:$B$32, "Offshore Wind")+SUMIFS($D$2:$D$32,$B$2:$B$32, "Onshore Wind")+SUMIFS($D$2:$D$32,$B$2:$B$32, "Sewage Gas")</f>
+        <v>30321.040000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="2">
+        <f>SUMIFS($J$2:$J$32,$B$2:$B$32, "Solar PV")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Offshore Wind")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Onshore Wind")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Sewage Gas")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="2">
+        <f>SUMIFS($J$2:$J$32,$B$2:$B$32, "Offshore Wind")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Onshore Wind")</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N30" xr:uid="{F4972E32-7E17-D640-8808-61170EE7E9D2}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="AC"/>
-        <filter val="Advanced Biofuel"/>
-        <filter val="Battery Storage"/>
-        <filter val="Biogas"/>
-        <filter val="Biomass"/>
-        <filter val="Data Centre"/>
-        <filter val="DC"/>
-        <filter val="Electricity"/>
-        <filter val="Embedded Solar"/>
-        <filter val="Embedded Wind"/>
-        <filter val="European Exports"/>
-        <filter val="European Imports"/>
-        <filter val="Landfill Gas"/>
-        <filter val="Large Hydro"/>
-        <filter val="Load Shedding"/>
-        <filter val="Offshore Wind"/>
-        <filter val="Onshore Wind"/>
-        <filter val="Pumped Storage Hydroelectricity"/>
-        <filter val="Sewage Gas"/>
-        <filter val="Small Hydro"/>
-        <filter val="Solar PV"/>
-        <filter val="Tidal Stream"/>
-        <filter val="Waste to Energy"/>
-        <filter val="Wave Power"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:N33" xr:uid="{F4972E32-7E17-D640-8808-61170EE7E9D2}"/>
   <mergeCells count="4">
     <mergeCell ref="A2:A23"/>
     <mergeCell ref="A24:A25"/>
@@ -2059,7 +2074,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{274D0A62-B14B-AA4E-B6C1-C6D101FC58CC}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.33203125" customWidth="1"/>
@@ -2107,7 +2122,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>12</v>
       </c>
@@ -2151,7 +2166,7 @@
         <v>83.809391000000005</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6"/>
       <c r="B3" s="1" t="s">
         <v>14</v>
@@ -2193,7 +2208,7 @@
         <v>66.732484999999997</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6"/>
       <c r="B4" s="1" t="s">
         <v>15</v>
@@ -2403,7 +2418,7 @@
         <v>66.331688</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6"/>
       <c r="B9" s="1" t="s">
         <v>20</v>
@@ -2445,7 +2460,7 @@
         <v>27.048884999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6"/>
       <c r="B10" s="1" t="s">
         <v>21</v>
@@ -2487,7 +2502,7 @@
         <v>66.732484999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
       <c r="B11" s="1" t="s">
         <v>22</v>
@@ -2529,7 +2544,7 @@
         <v>66.683919000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6"/>
       <c r="B12" s="1" t="s">
         <v>23</v>
@@ -2571,7 +2586,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="1" t="s">
         <v>25</v>
@@ -2781,7 +2796,7 @@
         <v>67.244376000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6"/>
       <c r="B18" s="1" t="s">
         <v>30</v>
@@ -2823,7 +2838,7 @@
         <v>66.732484999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6"/>
       <c r="B19" s="1" t="s">
         <v>31</v>
@@ -2907,7 +2922,7 @@
         <v>66.499548000000004</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6"/>
       <c r="B21" s="1" t="s">
         <v>33</v>
@@ -2949,7 +2964,7 @@
         <v>66.613305999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6"/>
       <c r="B22" s="1" t="s">
         <v>34</v>
@@ -2991,7 +3006,7 @@
         <v>66.732484999999997</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="7"/>
       <c r="B23" s="1" t="s">
         <v>35</v>
@@ -3033,7 +3048,7 @@
         <v>66.562911</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>36</v>
       </c>
@@ -3077,7 +3092,7 @@
         <v>-28.773026000000002</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6"/>
       <c r="B25" s="1" t="s">
         <v>38</v>
@@ -3119,7 +3134,7 @@
         <v>-9.8553840000000008</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="7"/>
       <c r="B26" s="1" t="s">
         <v>39</v>
@@ -3161,7 +3176,7 @@
         <v>-84.741156000000004</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>40</v>
       </c>
@@ -3205,7 +3220,7 @@
         <v>-66.750617000000005</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6"/>
       <c r="B28" s="1" t="s">
         <v>42</v>
@@ -3247,7 +3262,7 @@
         <v>-66.991299999999995</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="7"/>
       <c r="B29" s="1" t="s">
         <v>43</v>
@@ -3333,7 +3348,7 @@
         <v>4.6455590000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" ht="30" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="7"/>
       <c r="B31" s="1" t="s">
         <v>46</v>
@@ -3375,7 +3390,7 @@
         <v>1.8446279999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H32" s="10"/>
       <c r="I32" s="15" t="s">
         <v>49</v>
@@ -3400,7 +3415,7 @@
         <v>1082.4307110000002</v>
       </c>
     </row>
-    <row r="33" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H33" s="11"/>
       <c r="I33" s="14" t="s">
         <v>50</v>
@@ -3410,7 +3425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="8:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H34" s="11"/>
       <c r="I34" s="14" t="s">
         <v>51</v>
@@ -3420,36 +3435,48 @@
         <v>0</v>
       </c>
     </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="2">
+        <f>SUMIFS($D$2:$D$32,$B$2:$B$32, "Solar PV")+SUMIFS($D$2:$D$32,$B$2:$B$32, "Offshore Wind")+SUMIFS($D$2:$D$32,$B$2:$B$32, "Onshore Wind")+SUMIFS($D$2:$D$32,$B$2:$B$32, "Sewage Gas")</f>
+        <v>30321.040000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="2">
+        <f>SUMIFS($J$2:$J$32,$B$2:$B$32, "Solar PV")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Offshore Wind")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Onshore Wind")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Sewage Gas")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="2">
+        <f>SUMIFS($J$2:$J$32,$B$2:$B$32, "Offshore Wind")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Onshore Wind")</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N31" xr:uid="{274D0A62-B14B-AA4E-B6C1-C6D101FC58CC}">
+  <autoFilter ref="A1:N34" xr:uid="{274D0A62-B14B-AA4E-B6C1-C6D101FC58CC}">
     <filterColumn colId="1">
       <filters>
-        <filter val="AC"/>
-        <filter val="Advanced Biofuel"/>
         <filter val="Battery Storage"/>
-        <filter val="Biogas"/>
-        <filter val="Biomass"/>
-        <filter val="Data Centre"/>
-        <filter val="DC"/>
-        <filter val="Electricity"/>
         <filter val="Embedded Solar"/>
         <filter val="Embedded Wind"/>
-        <filter val="European Exports"/>
-        <filter val="European Imports"/>
-        <filter val="Landfill Gas"/>
-        <filter val="Large Hydro"/>
-        <filter val="Load Shedding"/>
-        <filter val="Nuclear"/>
         <filter val="Offshore Wind"/>
         <filter val="Onshore Wind"/>
-        <filter val="Pumped Storage Hydroelectricity"/>
-        <filter val="Sewage Gas"/>
-        <filter val="Small Hydro"/>
         <filter val="Solar PV"/>
-        <filter val="Tidal Stream"/>
-        <filter val="Virtual Link"/>
-        <filter val="Waste to Energy"/>
-        <filter val="Wave Power"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -3460,16 +3487,16 @@
     <mergeCell ref="A30:A31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D4BF803-EC4E-F842-B68E-528EC71F1DE9}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16.1640625" customWidth="1"/>
     <col min="3" max="3" width="19.1640625" customWidth="1"/>
     <col min="4" max="4" width="14.6640625" customWidth="1"/>
     <col min="5" max="5" width="13.5" customWidth="1"/>
@@ -3652,7 +3679,7 @@
         <v>77.292428000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
       <c r="B5" s="1" t="s">
         <v>16</v>
@@ -3694,7 +3721,7 @@
         <v>84.756013999999993</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="30" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="6"/>
       <c r="B6" s="1" t="s">
         <v>17</v>
@@ -3706,34 +3733,34 @@
         <v>29673</v>
       </c>
       <c r="E6" s="3">
-        <v>173070500</v>
+        <v>173069200</v>
       </c>
       <c r="F6" s="3">
         <v>0</v>
       </c>
       <c r="G6" s="3">
-        <v>173070500</v>
+        <v>173069200</v>
       </c>
       <c r="H6" s="3">
         <v>0</v>
       </c>
       <c r="I6" s="4">
-        <v>0.66400199999999998</v>
+        <v>0.66399699999999995</v>
       </c>
       <c r="J6" s="3">
-        <v>87577180</v>
+        <v>87578450</v>
       </c>
       <c r="K6" s="4">
         <v>0</v>
       </c>
       <c r="L6" s="3">
-        <v>11417110000</v>
+        <v>11417030000</v>
       </c>
       <c r="M6" s="3">
-        <v>11575430000</v>
+        <v>11575340000</v>
       </c>
       <c r="N6" s="4">
-        <v>66.882746999999995</v>
+        <v>66.882754000000006</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -3988,7 +4015,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="1" t="s">
         <v>25</v>
@@ -4072,7 +4099,7 @@
         <v>66.213396000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
       <c r="B15" s="1" t="s">
         <v>27</v>
@@ -4156,7 +4183,7 @@
         <v>66.219993000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="30" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
       <c r="B17" s="1" t="s">
         <v>29</v>
@@ -4168,34 +4195,34 @@
         <v>1302.3699999999999</v>
       </c>
       <c r="E17" s="3">
-        <v>6957449</v>
+        <v>6958719</v>
       </c>
       <c r="F17" s="3">
         <v>0</v>
       </c>
       <c r="G17" s="3">
-        <v>6957449</v>
+        <v>6958719</v>
       </c>
       <c r="H17" s="3">
         <v>0</v>
       </c>
       <c r="I17" s="4">
-        <v>0.60816800000000004</v>
+        <v>0.60827900000000001</v>
       </c>
       <c r="J17" s="3">
-        <v>4482569</v>
+        <v>4481299</v>
       </c>
       <c r="K17" s="4">
         <v>0</v>
       </c>
       <c r="L17" s="3">
-        <v>458969000</v>
+        <v>459052800</v>
       </c>
       <c r="M17" s="3">
-        <v>465917600</v>
+        <v>466001400</v>
       </c>
       <c r="N17" s="4">
-        <v>66.966724999999997</v>
+        <v>66.966543000000001</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
@@ -4464,22 +4491,22 @@
         <v>171000</v>
       </c>
       <c r="E24" s="3">
-        <v>272851900</v>
+        <v>272702000</v>
       </c>
       <c r="F24" s="3">
-        <v>662772100</v>
+        <v>662641300</v>
       </c>
       <c r="G24" s="3">
-        <v>-389920100</v>
+        <v>-389939300</v>
       </c>
       <c r="H24" s="3">
-        <v>389920100</v>
+        <v>389939300</v>
       </c>
       <c r="I24" s="4">
-        <v>0.622892</v>
+        <v>0.62270499999999995</v>
       </c>
       <c r="J24" s="3">
-        <v>1112144000</v>
+        <v>1112125000</v>
       </c>
       <c r="K24" s="4">
         <v>0</v>
@@ -4488,10 +4515,10 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
-        <v>-25968100000</v>
+        <v>-25967630000</v>
       </c>
       <c r="N24" s="4">
-        <v>-27.754849</v>
+        <v>-27.762678999999999</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
@@ -4506,22 +4533,22 @@
         <v>31513</v>
       </c>
       <c r="E25" s="3">
-        <v>62872090</v>
+        <v>62873860</v>
       </c>
       <c r="F25" s="3">
-        <v>66826660</v>
+        <v>66929710</v>
       </c>
       <c r="G25" s="3">
-        <v>-3954563</v>
+        <v>-4055847</v>
       </c>
       <c r="H25" s="3">
-        <v>3954563</v>
+        <v>4055847</v>
       </c>
       <c r="I25" s="4">
-        <v>0.46854800000000002</v>
+        <v>0.46892600000000001</v>
       </c>
       <c r="J25" s="3">
-        <v>272855600</v>
+        <v>272754300</v>
       </c>
       <c r="K25" s="4">
         <v>0</v>
@@ -4530,10 +4557,10 @@
         <v>0</v>
       </c>
       <c r="M25" s="3">
-        <v>-302637800</v>
+        <v>-310814700</v>
       </c>
       <c r="N25" s="4">
-        <v>-2.3333900000000001</v>
+        <v>-2.394501</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
@@ -4572,10 +4599,10 @@
         <v>11.93622</v>
       </c>
       <c r="M26" s="3">
-        <v>-64914900</v>
+        <v>-64917930</v>
       </c>
       <c r="N26" s="4">
-        <v>-54.384782000000001</v>
+        <v>-54.387321999999998</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
@@ -4818,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="4">
-        <v>0.99947399999999997</v>
+        <v>0.999475</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -4836,31 +4863,31 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="9:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="I33" s="15" t="s">
         <v>49</v>
       </c>
       <c r="J33" s="13">
         <f>SUM(J2:J32)</f>
-        <v>335696212999</v>
+        <v>335696092699</v>
       </c>
       <c r="K33" s="8" t="s">
         <v>52</v>
       </c>
       <c r="L33" s="2">
         <f>SUM(L3:L32)</f>
-        <v>14458371681.93622</v>
+        <v>14458375481.93622</v>
       </c>
       <c r="M33" s="2">
         <f>SUM(M3:M32)</f>
-        <v>-27013889570</v>
+        <v>-27021605700</v>
       </c>
       <c r="N33" s="2">
         <f>SUM(N3:N32)</f>
-        <v>1035.064734</v>
-      </c>
-    </row>
-    <row r="34" spans="9:14" x14ac:dyDescent="0.2">
+        <v>1034.9930780000002</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="I34" s="14" t="s">
         <v>50</v>
       </c>
@@ -4869,47 +4896,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="9:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="I35" s="14" t="s">
         <v>51</v>
       </c>
       <c r="J35" s="12">
-        <f>SUM(J22)</f>
+        <f>SUM(J20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="2">
+        <f>SUMIFS($D$2:$D$32,$B$2:$B$32, "Solar PV")+SUMIFS($D$2:$D$32,$B$2:$B$32, "Offshore Wind")+SUMIFS($D$2:$D$32,$B$2:$B$32, "Onshore Wind")+SUMIFS($D$2:$D$32,$B$2:$B$32, "Sewage Gas")</f>
+        <v>30321.040000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="2">
+        <f>SUMIFS($J$2:$J$32,$B$2:$B$32, "Solar PV")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Offshore Wind")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Onshore Wind")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Sewage Gas")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="2">
+        <f>SUMIFS($J$2:$J$32,$B$2:$B$32, "Offshore Wind")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Onshore Wind")</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N32" xr:uid="{4D4BF803-EC4E-F842-B68E-528EC71F1DE9}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="AC"/>
-        <filter val="Advanced Biofuel"/>
-        <filter val="Battery Storage"/>
-        <filter val="Biogas"/>
-        <filter val="Biomass"/>
-        <filter val="Data Centre"/>
-        <filter val="DC"/>
-        <filter val="DSM"/>
-        <filter val="Electricity"/>
-        <filter val="Embedded Solar"/>
-        <filter val="Embedded Wind"/>
-        <filter val="European Exports"/>
-        <filter val="European Imports"/>
-        <filter val="Landfill Gas"/>
-        <filter val="Large Hydro"/>
-        <filter val="Load Shedding"/>
-        <filter val="Offshore Wind"/>
-        <filter val="Onshore Wind"/>
-        <filter val="Pumped Storage Hydroelectricity"/>
-        <filter val="Sewage Gas"/>
-        <filter val="Small Hydro"/>
-        <filter val="Solar PV"/>
-        <filter val="Tidal Stream"/>
-        <filter val="Waste to Energy"/>
-        <filter val="Wave Power"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:N35" xr:uid="{4D4BF803-EC4E-F842-B68E-528EC71F1DE9}"/>
   <mergeCells count="4">
     <mergeCell ref="A2:A23"/>
     <mergeCell ref="A24:A26"/>
@@ -4923,7 +4952,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B4D27E0-A6E7-0A4E-A9C8-EA69BF34BB6E}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="17.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.6640625" customWidth="1"/>
@@ -6358,11 +6387,41 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>53</v>
+      </c>
       <c r="I36" s="14" t="s">
         <v>51</v>
       </c>
       <c r="J36" s="12">
         <f>SUM(J20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="2">
+        <f>SUMIFS($D$2:$D$32,$B$2:$B$32, "Solar PV")+SUMIFS($D$2:$D$32,$B$2:$B$32, "Offshore Wind")+SUMIFS($D$2:$D$32,$B$2:$B$32, "Onshore Wind")+SUMIFS($D$2:$D$32,$B$2:$B$32, "Sewage Gas")</f>
+        <v>30321.040000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="2">
+        <f>SUMIFS($J$2:$J$32,$B$2:$B$32, "Solar PV")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Offshore Wind")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Onshore Wind")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Sewage Gas")</f>
+        <v>440956.8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="2">
+        <f>SUMIFS($J$2:$J$32,$B$2:$B$32, "Offshore Wind")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Onshore Wind")</f>
         <v>0</v>
       </c>
     </row>
